--- a/medford_ik_izluchateli.xlsx
+++ b/medford_ik_izluchateli.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ИК излучатели для оснащения клиник и медицинских учреждений. В каталоге представлено 1 позиций.</t>
+          <t>ИК излучатели для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_ik_izluchateli.xlsx
+++ b/medford_ik_izluchateli.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать иК излучатели для клиники?</t>
+          <t>Что такое ИК излучатель?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (технические параметры). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>ИК излучатель — устройство, которое генерирует электромагнитное излучение в инфракрасном диапазоне (примерно 0,75–1000 мкм). Глазом это излучение не видно, но воспринимается как тепло. Принцип действия основан на преобразовании электрической или тепловой энергии в инфракрасное излучение нагретым элементом или ИК-источником.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Как ИК излучатель применяют в медицине?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>В медицине инфракрасные аппараты используют для физиотерапевтического прогрева тканей. Длинноволновое излучение проникает на несколько сантиметров и обеспечивает мягкое глубокое тепло. Показания к процедуре, её длительность и параметры определяет врач, поскольку тепловое воздействие подходит не при всех состояниях.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Чем медицинский ИК-аппарат отличается от обогревателя?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Медицинский физиотерапевтический аппарат предназначен для контролируемого прогрева тканей по назначению врача и является зарегистрированным медицинским изделием. Бытовой ИК-обогреватель греет помещение и к медицинскому применению не относится. Внешнее сходство не делает их взаимозаменяемыми: задачи, режимы и требования к безопасности разные.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какие бывают виды ИК-излучения?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>По спектру инфракрасное излучение делят на коротковолновое (ближнее, поверхностное воздействие), средневолновое и длинноволновое (дальнее, проникает на несколько сантиметров). Для медицинского прогрева чаще применяют длинноволновый диапазон. Конкретный спектр аппарата уточняют по паспорту производителя.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Есть ли противопоказания к прогреву?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Тепловое физиотерапевтическое воздействие показано не всегда: существуют состояния, при которых прогрев противопоказан. Поэтому назначение процедуры, определение режима и оценку противопоказаний проводит врач. Самостоятельно назначать себе физиопроцедуры на медицинском ИК-аппарате не следует.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>В чем минус инфракрасного обогревателя?</t>
+          <t>Нужна ли регистрация Росздравнадзора?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Для применения в клинике инфракрасный физиотерапевтический аппарат должен быть зарегистрированным медицинским изделием с действующим регистрационным удостоверением. Статус регистрации подтверждают до покупки — это условие законной эксплуатации в лечебном учреждении и одно из отличий медицинского прибора от бытового.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Что такое инфракрасное излучение простыми словами?</t>
+          <t>Какие параметры уточнять при выборе?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Уточняют спектр (диапазон длин волн), режимы работы и управление, наличие таймера и защиты от перегрева, а также эргономику для кабинета. Технические характеристики берут из паспорта конкретной модели. Мощность и глубину воздействия рассматривают в связке с назначением, а не как единственный критерий.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ИК излучатели для оснащения клиник и медицинских учреждений.</t>
+          <t>ИК излучатели — устройства, генерирующие инфракрасное излучение, которое ткани воспринимают как тепло. В медицине такие аппараты применяют для физиотерапевтического прогрева. В категории представлен физиотерапевтический инфракрасный аппарат Chammed XCS5 Extreme. Инфракрасный диапазон охватывает длины волн примерно от 0,75 до 1000 мкм; для человеческого глаза это излучение невидимо. Длинноволновое ИК проникает в ткани на несколько сантиметров и обеспечивает мягкий глубокий прогрев.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Виды ИК-излучения по спектру</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое иК излучатели</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -2928,43 +2928,92 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Виды ИК-излучения по спектру</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Диапазон</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Проникновение</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Характеристика</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Аппарат физиотерапевтический (инфракрасный) Chammed XCS5 Extreme</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Коротковолновое (ближнее)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>поверхностный слой</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>наибольшая энергия</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Средневолновое</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>немного глубже</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>промежуточный прогрев</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Длинноволновое (дальнее)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>несколько сантиметров</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>мягкий глубокий прогрев, применяется в медицине</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2976,7 +3025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3302,12 +3351,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Разделите медицинское и бытовое</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается иК излучатели: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Сначала фиксируют, что нужен именно медицинский физиотерапевтический аппарат, а не бытовой ИК-обогреватель. Внешне похожие устройства решают разные задачи: обогреватель греет помещение, медицинский ИК-аппарат обеспечивает контролируемый прогрев тканей. Для клиники подходит только зарегистрированное медицинское изделие.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3347,12 +3396,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Определите задачи кабинета</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Уточняют, для каких процедур нужен аппарат и с какой интенсивностью он будет использоваться. От этого зависят требования к режимам, управлению и эргономике. Модель, например Chammed XCS5 Extreme, подбирают под профиль физиотерапевтического или ЛОР-кабинета, где прогрев назначается врачом.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3392,12 +3441,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Уточните спектр и режимы</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: технические характеристики. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Инфракрасное излучение делят на коротко-, средне- и длинноволновое; в медицине для глубокого мягкого прогрева чаще используют длинноволновый диапазон. Конкретный спектр и режимы аппарата сверяют по паспорту производителя, а не по общим описаниям, чтобы соответствие задаче было подтверждено документально.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3437,12 +3486,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените управление и безопасность</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Важны регулировка режима, таймер и стабильность прогрева, а также защита от перегрева. Управляемость позволяет выдерживать назначенные врачом параметры процедуры. Требования к безопасности и допустимым режимам уточняют по инструкции, поскольку тепловое воздействие подходит не при всех состояниях.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3482,12 +3531,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте регистрацию</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Для применения в клинике аппарат должен быть зарегистрированным медицинским изделием с действующим регистрационным удостоверением Росздравнадзора. Статус регистрации уточняют до покупки — это условие законной эксплуатации в лечебном учреждении и отличие медицинского прибора от бытового устройства.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3527,12 +3576,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Согласуйте гарантию и сервис</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Заранее уточняют условия гарантии, доступность запчастей и порядок обслуживания. Для аппарата, включённого в поток кабинета, важно, чтобы ремонт и поставка комплектующих не приводили к длительным простоям. Эти условия согласуют одновременно с выбором модели.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3582,7 +3631,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ИК излучатели подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на ключевые технические характеристики, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Медицинский инфракрасный аппарат — это не бытовой обогреватель, и путать их нельзя. В физиотерапии значение имеют спектр, управляемость режима и предсказуемость прогрева, а не просто мощность нагрева воздуха. Назначение процедуры, её длительность и противопоказания определяет врач: тепловое воздействие уместно не во всех случаях, поэтому аппарат подбирают под задачи физиотерапевтического кабинета, а не как источник тепла.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3866,13 +3915,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое иК излучатели</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ИК излучатели — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>ИК излучатель — устройство, преобразующее электрическую или тепловую энергию в инфракрасное излучение, которое ткани воспринимают как тепло. Инфракрасный диапазон охватывает длины волн примерно от 0,75 до 1000 мкм и глазом не виден. В медицине инфракрасные аппараты используют для физиотерапевтического прогрева: длинноволновое излучение проникает на несколько сантиметров и даёт мягкое глубокое тепло. Медицинский ИК-аппарат, например Chammed XCS5 Extreme, отличается от бытовых обогревателей назначением и режимами. Показания, длительность и параметры процедуры определяет врач; самостоятельно назначать физиопроцедуры не следует.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3909,13 +3958,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>ИК излучатели в медицине</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (технические параметры), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>В медицине инфракрасные излучатели применяют для физиотерапевтического прогрева тканей. Инфракрасное излучение с длиной волны примерно от 0,75 до 1000 мкм воспринимается как тепло и глазом не видно. Длинноволновый диапазон проникает вглубь на несколько сантиметров, что используют для мягкого прогрева по назначению врача в физиотерапевтических и ЛОР-кабинетах.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3952,13 +4001,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Как работает инфракрасный аппарат</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Принцип действия основан на преобразовании электрической или тепловой энергии в инфракрасное излучение нагревательным элементом или ИК-источником. Спектр излучения зависит от конструкции и определяет глубину прогрева: коротковолновое воздействует поверхностно, длинноволновое — глубже. Управляемость режима позволяет выдерживать параметры процедуры, назначенные врачом.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -3995,13 +4044,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Медицинский аппарат и бытовой обогреватель</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Медицинский физиотерапевтический ИК-аппарат и бытовой обогреватель — разные устройства. Первый предназначен для контролируемого прогрева тканей и является зарегистрированным медицинским изделием, второй греет помещение. Смешивать их характеристики и назначение некорректно: для клиники подходит только медицинский прибор с подтверждённой регистрацией.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4018,6 +4067,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Выбор и безопасность</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>При подборе инфракрасного аппарата для кабинета учитывают спектр, режимы работы, управление, таймер и защиту от перегрева, а также наличие регистрационного удостоверения Росздравнадзора. Поскольку тепловое воздействие имеет противопоказания, назначение и параметры процедуры определяет врач. Технические данные сверяют по паспорту конкретной модели.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>ik_izluchateli</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
